--- a/artfynd/S 270-2023 artfynd.xlsx
+++ b/artfynd/S 270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575705</t>
         </is>
       </c>
     </row>
@@ -988,6 +1003,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80651764</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575640</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575696</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575699</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108670588</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124001589</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575702</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575703</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575704</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575707</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575708</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575709</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575710</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575713</t>
         </is>
       </c>
     </row>
@@ -2568,8 +2658,33 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80651765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>